--- a/registry_big.xlsx
+++ b/registry_big.xlsx
@@ -1843,7 +1843,7 @@
     <row r="1" ht="35.05" customHeight="1" s="4">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PRJ-101</t>
+          <t>C1-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PRJ-102</t>
+          <t>C1-102</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2064,7 +2064,7 @@
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PRJ-103</t>
+          <t>C1-103</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="1" ht="35.05" customHeight="1" s="4">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>c1_human_id</t>
+          <t>c1_id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2215,12 +2215,12 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PRJ-101</t>
+          <t>C1-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>APP-101</t>
+          <t>C2-101</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PRJ-101</t>
+          <t>C1-101</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>APP-102</t>
+          <t>C2-102</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2324,12 +2324,12 @@
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PRJ-101</t>
+          <t>C1-101</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>APP-103</t>
+          <t>C2-103</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRJ-102</t>
+          <t>C1-102</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>APP-201</t>
+          <t>C2-201</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2438,12 +2438,12 @@
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PRJ-102</t>
+          <t>C1-102</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>APP-202</t>
+          <t>C2-202</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2495,12 +2495,12 @@
     <row r="7" ht="15" customHeight="1" s="4">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PRJ-103</t>
+          <t>C1-103</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>APP-301</t>
+          <t>C2-301</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2552,12 +2552,12 @@
     <row r="8" ht="15" customHeight="1" s="4">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PRJ-999</t>
+          <t>C1-999</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>APP-ORPH-9</t>
+          <t>C2-ORPH-9</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="1" ht="35.05" customHeight="1" s="4">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>c2_human_id</t>
+          <t>c2_id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>APP-101</t>
+          <t>C2-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>CMP-101</t>
+          <t>C3-101</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -2790,12 +2790,12 @@
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>APP-101</t>
+          <t>C2-101</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>CMP-102</t>
+          <t>C3-102</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2857,12 +2857,12 @@
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>APP-101</t>
+          <t>C2-101</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>CMP-103</t>
+          <t>C3-103</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2914,12 +2914,12 @@
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>APP-102</t>
+          <t>C2-102</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CMP-111</t>
+          <t>C3-111</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2981,12 +2981,12 @@
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>APP-102</t>
+          <t>C2-102</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>CMP-112</t>
+          <t>C3-112</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3038,12 +3038,12 @@
     <row r="7" ht="15" customHeight="1" s="4">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>APP-201</t>
+          <t>C2-201</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CMP-201</t>
+          <t>C3-201</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3100,12 +3100,12 @@
     <row r="8" ht="15" customHeight="1" s="4">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>APP-201</t>
+          <t>C2-201</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CMP-202</t>
+          <t>C3-202</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3157,12 +3157,12 @@
     <row r="9" ht="15" customHeight="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>APP-301</t>
+          <t>C2-301</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CMP-301</t>
+          <t>C3-301</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3229,12 +3229,12 @@
     <row r="10" ht="15" customHeight="1" s="4">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>APP-301</t>
+          <t>C2-301</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CMP-302</t>
+          <t>C3-302</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3291,12 +3291,12 @@
     <row r="11" ht="15" customHeight="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>APP-999</t>
+          <t>C2-999</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CMP-ORPH-9</t>
+          <t>C3-ORPH-9</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3348,12 +3348,12 @@
     <row r="12" ht="15" customHeight="1" s="4">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>APP-101</t>
+          <t>C2-101</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CMP-104</t>
+          <t>C3-104</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3438,12 +3438,12 @@
     <row r="1" ht="35.05" customHeight="1" s="4">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>c3_human_id</t>
+          <t>c3_id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -3530,12 +3530,12 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CMP-101</t>
+          <t>C3-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>RUN-101</t>
+          <t>C4-101</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -3612,12 +3612,12 @@
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CMP-101</t>
+          <t>C3-101</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>RUN-102</t>
+          <t>C4-102</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3689,12 +3689,12 @@
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CMP-102</t>
+          <t>C3-102</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>RUN-103</t>
+          <t>C4-103</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>CMP-103</t>
+          <t>C3-103</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>RUN-104</t>
+          <t>C4-104</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>CMP-111</t>
+          <t>C3-111</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>RUN-111</t>
+          <t>C4-111</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3925,12 +3925,12 @@
     <row r="7" ht="15" customHeight="1" s="4">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>CMP-112</t>
+          <t>C3-112</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RUN-112</t>
+          <t>C4-112</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="8" ht="15" customHeight="1" s="4">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>CMP-301</t>
+          <t>C3-301</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RUN-301</t>
+          <t>C4-301</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -4084,12 +4084,12 @@
     <row r="9" ht="15" customHeight="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>CMP-301</t>
+          <t>C3-301</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>RUN-302</t>
+          <t>C4-302</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -4161,12 +4161,12 @@
     <row r="10" ht="15" customHeight="1" s="4">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>CMP-302</t>
+          <t>C3-302</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>RUN-303</t>
+          <t>C4-303</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="11" ht="15" customHeight="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>CMP-999</t>
+          <t>C3-999</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>RUN-ORPH-9</t>
+          <t>C4-ORPH-9</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
